--- a/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/03_Matriz-de-distribucion.xlsx
+++ b/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/03_Matriz-de-distribucion.xlsx
@@ -82,7 +82,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -134,8 +134,44 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+        <bgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -157,11 +193,55 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,6 +353,53 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,6 +868,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
@@ -764,6 +892,13 @@
           <t>PRODUCTO</t>
         </is>
       </c>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="39" t="n"/>
       <c r="K14" s="10" t="inlineStr">
         <is>
           <t>CASO</t>
@@ -791,6 +926,13 @@
           <t>Informe de descripción de la matriz de aspectos e impactos + hoja de trabajo + PPT · Mantenimiento y Servicios Automotrices S.A.C. · fuente: Coblentz Pineda (2023), UNFV</t>
         </is>
       </c>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="39" t="n"/>
       <c r="K15" s="12" t="inlineStr">
         <is>
           <t>único</t>
@@ -818,6 +960,13 @@
           <t>Informe de descripción del manejo de residuos + hoja de trabajo + PPT · la misma empresa, un año después · fuente: Coblentz Pineda (2023), UNFV</t>
         </is>
       </c>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="38" t="n"/>
+      <c r="H16" s="38" t="n"/>
+      <c r="I16" s="38" t="n"/>
+      <c r="J16" s="39" t="n"/>
       <c r="K16" s="16" t="inlineStr">
         <is>
           <t>único</t>
@@ -829,6 +978,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -899,749 +1049,750 @@
       </c>
     </row>
     <row r="20" ht="40.05" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Bloque 1</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="40" t="inlineStr">
         <is>
           <t>Adquisición</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>IND-1</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Aspectos, impactos y controles ambientales</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>Describe en qué se diferencia un aspecto ambiental de un impacto ambiental, y sobre cuál de los dos actúa el control que registra la matriz.</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="40" t="inlineStr">
         <is>
           <t>TC1 · c1</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="43" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>3 pk</t>
+        </is>
+      </c>
+      <c r="L20" s="43" t="inlineStr">
+        <is>
+          <t>30 láms</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40.05" customHeight="1">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>Bloque 1</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>IND-1</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>Identificación de aspectos ambientales: actividad, entrada y salida</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>Describe cómo se identifican los aspectos ambientales de una actividad a partir de sus entradas y salidas, y qué cambia en el resultado cuando la actividad se descompone con más o con menos detalle.</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>TC1 · c1</t>
+        </is>
+      </c>
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="I21" s="43" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40.05" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="J21" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40.05" customHeight="1">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Bloque 1</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>Adquisición</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D22" s="40" t="inlineStr">
         <is>
           <t>IND-1</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>Identificación de aspectos ambientales: actividad, entrada y salida</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>Describe cómo se identifican los aspectos ambientales de una actividad a partir de sus entradas y salidas, y qué cambia en el resultado cuando la actividad se descompone con más o con menos detalle.</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>TC1 · c1</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40.05" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>Condición operativa, tipo de actividad y requisitos legales</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>Describe cómo la condición operativa —normal, anormal y de emergencia—, el tipo de actividad —pasada, presente o futura— y el requisito legal aplicable cambian el registro de un mismo aspecto ambiental en la matriz.</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>TC1 · c2</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40.05" customHeight="1">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Bloque 1</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>Adquisición</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="40" t="inlineStr">
         <is>
           <t>IND-1</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>Condición operativa, tipo de actividad y requisitos legales</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>Describe cómo la condición operativa —normal, anormal y de emergencia—, el tipo de actividad —pasada, presente o futura— y el requisito legal aplicable cambian el registro de un mismo aspecto ambiental en la matriz.</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Evaluación de impactos: severidad, probabilidad y nivel de impacto</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr">
+        <is>
+          <t>Describe cómo se obtiene el nivel de impacto de un aspecto ambiental a partir de su severidad y su probabilidad.</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>TC1 · c2</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40.05" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40.05" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Bloque 1</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
         <is>
           <t>Adquisición</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="40" t="inlineStr">
         <is>
           <t>IND-1</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>Evaluación de impactos: severidad, probabilidad y nivel de impacto</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>Describe cómo se obtiene el nivel de impacto de un aspecto ambiental a partir de su severidad y su probabilidad.</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>TC1 · c2</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40.05" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="E24" s="42" t="inlineStr">
+        <is>
+          <t>Aspectos ambientales significativos por sector productivo</t>
+        </is>
+      </c>
+      <c r="F24" s="42" t="inlineStr">
+        <is>
+          <t>Describe qué condición hace que un aspecto ambiental se declare significativo, y cómo esa condición cambia entre una operación minera, industrial, de construcción y cementera.</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>TC1 · c3</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40.05" customHeight="1">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t>Bloque 1</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="inlineStr">
+        <is>
+          <t>Evaluación</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="inlineStr">
+        <is>
+          <t>IND-1</t>
+        </is>
+      </c>
+      <c r="E25" s="47" t="inlineStr">
+        <is>
+          <t>TC1 · sustentación</t>
+        </is>
+      </c>
+      <c r="F25" s="48" t="inlineStr">
+        <is>
+          <t>— pendiente —</t>
+        </is>
+      </c>
+      <c r="G25" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40.05" customHeight="1">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
         <is>
           <t>Adquisición</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>IND-1</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>Aspectos ambientales significativos por sector productivo</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>Describe qué condición hace que un aspecto ambiental se declare significativo, y cómo esa condición cambia entre una operación minera, industrial, de construcción y cementera.</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>TC1 · c3</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40.05" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Bloque 1</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="D26" s="50" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E26" s="52" t="inlineStr">
+        <is>
+          <t>Marco normativo y clasificación de los residuos sólidos</t>
+        </is>
+      </c>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>Describe cómo la ley define y clasifica un residuo sólido en sus dos ejes —peligroso o no peligroso, municipal o no municipal— y qué orden impone la jerarquía de la gestión integral.</t>
+        </is>
+      </c>
+      <c r="G26" s="50" t="inlineStr">
+        <is>
+          <t>TC2 · c1</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40.05" customHeight="1">
+      <c r="A27" s="50" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="D27" s="50" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E27" s="52" t="inlineStr">
+        <is>
+          <t>Operaciones del manejo y segregación según la NTP 900.058:2019</t>
+        </is>
+      </c>
+      <c r="F27" s="52" t="inlineStr">
+        <is>
+          <t>Describe las nueve operaciones del manejo de residuos sólidos, desde la caracterización hasta el transporte, y qué código de colores corresponde al ámbito municipal y cuál al no municipal.</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="inlineStr">
+        <is>
+          <t>TC2 · c1</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40.05" customHeight="1">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>S9</t>
+        </is>
+      </c>
+      <c r="C28" s="50" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>Manejo de residuos peligrosos en los sectores industrial, salud y construcción</t>
+        </is>
+      </c>
+      <c r="F28" s="52" t="inlineStr">
+        <is>
+          <t>Describe cómo se maneja un residuo peligroso no municipal y qué cambia en ese manejo entre el sector industrial, el de salud y el de construcción.</t>
+        </is>
+      </c>
+      <c r="G28" s="50" t="inlineStr">
+        <is>
+          <t>TC2 · c2</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40.05" customHeight="1">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C29" s="50" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="D29" s="50" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E29" s="52" t="inlineStr">
+        <is>
+          <t>Régimen especial de gestión y manejo de RAEE</t>
+        </is>
+      </c>
+      <c r="F29" s="52" t="inlineStr">
+        <is>
+          <t>Describe qué es un RAEE, en qué categorías se clasifica y qué contiene el plan de manejo que exige su régimen especial.</t>
+        </is>
+      </c>
+      <c r="G29" s="50" t="inlineStr">
+        <is>
+          <t>TC2 · c2</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40.05" customHeight="1">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C30" s="50" t="inlineStr">
+        <is>
+          <t>Adquisición</t>
+        </is>
+      </c>
+      <c r="D30" s="50" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E30" s="52" t="inlineStr">
+        <is>
+          <t>Infraestructuras de disposición final y empresas operadoras (EO-RS)</t>
+        </is>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>Describe en qué se diferencian un relleno sanitario, un relleno de seguridad y un botadero, y qué exige la ley a la empresa operadora que dispone el residuo.</t>
+        </is>
+      </c>
+      <c r="G30" s="50" t="inlineStr">
+        <is>
+          <t>TC2 · c3</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40.05" customHeight="1">
+      <c r="A31" s="45" t="inlineStr">
+        <is>
+          <t>Bloque 2</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C31" s="45" t="inlineStr">
         <is>
           <t>Evaluación</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>IND-1</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>TC1 · sustentación</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="D31" s="45" t="inlineStr">
+        <is>
+          <t>IND-2</t>
+        </is>
+      </c>
+      <c r="E31" s="47" t="inlineStr">
+        <is>
+          <t>TC2 · sustentación</t>
+        </is>
+      </c>
+      <c r="F31" s="48" t="inlineStr">
         <is>
           <t>— pendiente —</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40.05" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>Marco normativo y clasificación de los residuos sólidos</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="inlineStr">
-        <is>
-          <t>Describe cómo la ley define y clasifica un residuo sólido en sus dos ejes —peligroso o no peligroso, municipal o no municipal— y qué orden impone la jerarquía de la gestión integral.</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>TC2 · c1</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40.05" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>Operaciones del manejo y segregación según la NTP 900.058:2019</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="inlineStr">
-        <is>
-          <t>Describe las nueve operaciones del manejo de residuos sólidos, desde la caracterización hasta el transporte, y qué código de colores corresponde al ámbito municipal y cuál al no municipal.</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>TC2 · c1</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40.05" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>Manejo de residuos peligrosos en los sectores industrial, salud y construcción</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>Describe cómo se maneja un residuo peligroso no municipal y qué cambia en ese manejo entre el sector industrial, el de salud y el de construcción.</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>TC2 · c2</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40.05" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>Régimen especial de gestión y manejo de RAEE</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>Describe qué es un RAEE, en qué categorías se clasifica y qué contiene el plan de manejo que exige su régimen especial.</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>TC2 · c2</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="40.05" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Adquisición</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>Infraestructuras de disposición final y empresas operadoras (EO-RS)</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>Describe en qué se diferencian un relleno sanitario, un relleno de seguridad y un botadero, y qué exige la ley a la empresa operadora que dispone el residuo.</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>TC2 · c3</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="40.05" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>Bloque 2</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>Evaluación</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>IND-2</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>TC2 · sustentación</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
-        <is>
-          <t>— pendiente —</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+      <c r="G31" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
@@ -1685,7 +1836,7 @@
           <t>10 de 10</t>
         </is>
       </c>
-      <c r="L35" s="31" t="n">
+      <c r="L35" s="53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1705,7 +1856,7 @@
           <t>2 de 10</t>
         </is>
       </c>
-      <c r="L36" s="32" t="n">
+      <c r="L36" s="54" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1725,7 +1876,7 @@
           <t>2 de 10</t>
         </is>
       </c>
-      <c r="L37" s="32" t="n">
+      <c r="L37" s="54" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1745,7 +1896,7 @@
           <t>1 de 10</t>
         </is>
       </c>
-      <c r="L38" s="32" t="n">
+      <c r="L38" s="54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1765,7 +1916,7 @@
           <t>1 de 10</t>
         </is>
       </c>
-      <c r="L39" s="32" t="n">
+      <c r="L39" s="54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1777,18 +1928,19 @@
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>······························</t>
+          <t>▉▉▉···························</t>
         </is>
       </c>
       <c r="K40" s="30" t="inlineStr">
         <is>
-          <t>0 de 10</t>
-        </is>
-      </c>
-      <c r="L40" s="33" t="n">
-        <v>0</v>
-      </c>
-    </row>
+          <t>1 de 10</t>
+        </is>
+      </c>
+      <c r="L40" s="54" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
         <is>
@@ -1832,6 +1984,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
